--- a/public/exports-60-250-with-coowners/29189366.xlsx
+++ b/public/exports-60-250-with-coowners/29189366.xlsx
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221046</t>
+          <t xml:space="preserve">311221033</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
